--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.78165</v>
+        <v>16.60046</v>
       </c>
       <c r="D2" t="n">
-        <v>16.48512</v>
+        <v>16.25876</v>
       </c>
       <c r="E2" t="n">
-        <v>16.40603</v>
+        <v>16.53048</v>
       </c>
       <c r="F2" t="n">
-        <v>42.22471</v>
+        <v>41.86547</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05085</v>
+        <v>0.04971</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80291</v>
+        <v>1.80232</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.95951</v>
+        <v>16.59211</v>
       </c>
       <c r="D3" t="n">
-        <v>16.4383</v>
+        <v>15.92194</v>
       </c>
       <c r="E3" t="n">
-        <v>16.37552</v>
+        <v>16.56609</v>
       </c>
       <c r="F3" t="n">
-        <v>42.98173</v>
+        <v>41.98954</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05002</v>
+        <v>0.0497</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84122</v>
+        <v>1.79762</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.60098</v>
+        <v>16.67099</v>
       </c>
       <c r="D4" t="n">
-        <v>16.75073</v>
+        <v>16.55596</v>
       </c>
       <c r="E4" t="n">
-        <v>16.64684</v>
+        <v>16.66549</v>
       </c>
       <c r="F4" t="n">
-        <v>42.70513</v>
+        <v>41.76639</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04987</v>
+        <v>0.05006</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8089</v>
+        <v>1.79451</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.35687</v>
+        <v>16.51751</v>
       </c>
       <c r="D6" t="n">
-        <v>16.10604</v>
+        <v>16.26826</v>
       </c>
       <c r="E6" t="n">
-        <v>16.2125</v>
+        <v>16.30912</v>
       </c>
       <c r="F6" t="n">
-        <v>21.89196</v>
+        <v>21.69349</v>
       </c>
       <c r="G6" t="n">
-        <v>34.54691</v>
+        <v>33.87913</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.61855</v>
+        <v>16.74847</v>
       </c>
       <c r="D7" t="n">
-        <v>16.32763</v>
+        <v>16.36171</v>
       </c>
       <c r="E7" t="n">
-        <v>16.2877</v>
+        <v>16.43349</v>
       </c>
       <c r="F7" t="n">
-        <v>22.21596</v>
+        <v>21.60631</v>
       </c>
       <c r="G7" t="n">
-        <v>34.89664</v>
+        <v>33.7146</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.59173</v>
+        <v>16.68684</v>
       </c>
       <c r="D8" t="n">
-        <v>15.86911</v>
+        <v>15.977</v>
       </c>
       <c r="E8" t="n">
-        <v>16.52404</v>
+        <v>16.41027</v>
       </c>
       <c r="F8" t="n">
-        <v>21.73745</v>
+        <v>21.52838</v>
       </c>
       <c r="G8" t="n">
-        <v>34.63867</v>
+        <v>34.53389</v>
       </c>
     </row>
   </sheetData>
